--- a/public/templates/OArm_Test_Data_Template_NoTimer.xlsx
+++ b/public/templates/OArm_Test_Data_Template_NoTimer.xlsx
@@ -561,7 +561,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>mA Station 1</v>
+        <v>mAs Station 1</v>
       </c>
       <c r="B6" t="str">
         <v>50</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>mA Station 2</v>
+        <v>mAs Station 2</v>
       </c>
       <c r="B7" t="str">
         <v>100</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>mA Station 3</v>
+        <v>mAs Station 3</v>
       </c>
       <c r="B8" t="str">
         <v>200</v>
